--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/93.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/93.xlsx
@@ -426,13 +426,13 @@
         <v>-4.512614582260623</v>
       </c>
       <c r="E2">
-        <v>-10.65392097932728</v>
+        <v>-7.946989413450258</v>
       </c>
       <c r="F2">
-        <v>-2.987363877883241</v>
+        <v>-2.975894302824079</v>
       </c>
       <c r="G2">
-        <v>-10.12145835141677</v>
+        <v>-9.17264391917994</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.95332537091191</v>
       </c>
       <c r="E3">
-        <v>-11.49071052036063</v>
+        <v>-10.14678623215629</v>
       </c>
       <c r="F3">
-        <v>-3.096624709945092</v>
+        <v>-2.648625394428258</v>
       </c>
       <c r="G3">
-        <v>-10.05996825939278</v>
+        <v>-8.846684088243142</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.545078383893351</v>
       </c>
       <c r="E4">
-        <v>-11.04929751646297</v>
+        <v>-9.395747874932175</v>
       </c>
       <c r="F4">
-        <v>-2.331162699346779</v>
+        <v>-2.583673934742152</v>
       </c>
       <c r="G4">
-        <v>-9.794822588838729</v>
+        <v>-8.406245718318878</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.358550898691123</v>
       </c>
       <c r="E5">
-        <v>-12.58249843276591</v>
+        <v>-10.38694932267908</v>
       </c>
       <c r="F5">
-        <v>-2.526460254965595</v>
+        <v>-2.454024495795196</v>
       </c>
       <c r="G5">
-        <v>-9.853241457483083</v>
+        <v>-8.055814536991743</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.347489966337216</v>
       </c>
       <c r="E6">
-        <v>-12.69837302567418</v>
+        <v>-11.31648653986353</v>
       </c>
       <c r="F6">
-        <v>-2.271939400251031</v>
+        <v>-2.462574904126892</v>
       </c>
       <c r="G6">
-        <v>-9.935819960469628</v>
+        <v>-8.521223002983382</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.478556859242046</v>
       </c>
       <c r="E7">
-        <v>-13.31440851578163</v>
+        <v>-11.43717037216795</v>
       </c>
       <c r="F7">
-        <v>-1.819538968723123</v>
+        <v>-2.189493649385201</v>
       </c>
       <c r="G7">
-        <v>-9.812203219439107</v>
+        <v>-7.904231944610075</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.689424993225864</v>
       </c>
       <c r="E8">
-        <v>-13.72950202874671</v>
+        <v>-12.9606350693544</v>
       </c>
       <c r="F8">
-        <v>-1.288387304945871</v>
+        <v>-1.870119910705463</v>
       </c>
       <c r="G8">
-        <v>-9.987666542330414</v>
+        <v>-8.227353518897953</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.915210586549577</v>
       </c>
       <c r="E9">
-        <v>-14.82620333545031</v>
+        <v>-12.97448314286986</v>
       </c>
       <c r="F9">
-        <v>-1.219274955795503</v>
+        <v>-1.620777180625798</v>
       </c>
       <c r="G9">
-        <v>-9.597004303462926</v>
+        <v>-9.48275216876306</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.084795426892398</v>
       </c>
       <c r="E10">
-        <v>-15.3283205334208</v>
+        <v>-14.29725492898438</v>
       </c>
       <c r="F10">
-        <v>-0.978128092799136</v>
+        <v>-1.318162142872097</v>
       </c>
       <c r="G10">
-        <v>-9.939800082221234</v>
+        <v>-8.143370653083965</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.133171830564612</v>
       </c>
       <c r="E11">
-        <v>-16.41790307898435</v>
+        <v>-14.23742925886904</v>
       </c>
       <c r="F11">
-        <v>-0.8464176757540146</v>
+        <v>-1.011918027526731</v>
       </c>
       <c r="G11">
-        <v>-9.31387097632</v>
+        <v>-8.330771060008532</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.010660436546114</v>
       </c>
       <c r="E12">
-        <v>-17.20307254480427</v>
+        <v>-15.53180751295547</v>
       </c>
       <c r="F12">
-        <v>-0.1590350914413736</v>
+        <v>-1.129272009113934</v>
       </c>
       <c r="G12">
-        <v>-8.924590131729039</v>
+        <v>-7.78477907373849</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.688635966004258</v>
       </c>
       <c r="E13">
-        <v>-17.12684021335915</v>
+        <v>-15.61529898823489</v>
       </c>
       <c r="F13">
-        <v>-0.3024727058079276</v>
+        <v>-0.4106525184091263</v>
       </c>
       <c r="G13">
-        <v>-8.201809209057675</v>
+        <v>-6.962088235803595</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.170541191684728</v>
       </c>
       <c r="E14">
-        <v>-17.86814235146677</v>
+        <v>-17.1349008970928</v>
       </c>
       <c r="F14">
-        <v>0.008955332744157702</v>
+        <v>-0.7597480795013107</v>
       </c>
       <c r="G14">
-        <v>-7.885296014990519</v>
+        <v>-6.873784001195819</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.487052364422329</v>
       </c>
       <c r="E15">
-        <v>-19.11605393376049</v>
+        <v>-17.3862266760445</v>
       </c>
       <c r="F15">
-        <v>0.5292346743596655</v>
+        <v>-0.7428419291775756</v>
       </c>
       <c r="G15">
-        <v>-7.639732674703237</v>
+        <v>-6.602945411236133</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.693028101542773</v>
       </c>
       <c r="E16">
-        <v>-19.58303923037947</v>
+        <v>-17.53747317942668</v>
       </c>
       <c r="F16">
-        <v>0.4934500309261298</v>
+        <v>-0.2370606738458647</v>
       </c>
       <c r="G16">
-        <v>-7.570393900709051</v>
+        <v>-6.281621946362831</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.8559372357463578</v>
       </c>
       <c r="E17">
-        <v>-20.24389302774083</v>
+        <v>-19.56754279232522</v>
       </c>
       <c r="F17">
-        <v>0.5025670425613411</v>
+        <v>0.3329853245950319</v>
       </c>
       <c r="G17">
-        <v>-6.8137442091011</v>
+        <v>-5.247354661053381</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.04368513174157478</v>
       </c>
       <c r="E18">
-        <v>-21.04315510467262</v>
+        <v>-19.81623752787846</v>
       </c>
       <c r="F18">
-        <v>0.9491705590044581</v>
+        <v>0.3716120965875729</v>
       </c>
       <c r="G18">
-        <v>-6.048084283090913</v>
+        <v>-4.195821587898133</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.683182246219231</v>
       </c>
       <c r="E19">
-        <v>-21.68445947974287</v>
+        <v>-21.40209101146859</v>
       </c>
       <c r="F19">
-        <v>1.161451303115471</v>
+        <v>0.1513997345947551</v>
       </c>
       <c r="G19">
-        <v>-5.486598368617173</v>
+        <v>-4.065137095628569</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.282396385006478</v>
       </c>
       <c r="E20">
-        <v>-23.1060652110748</v>
+        <v>-21.51269446063193</v>
       </c>
       <c r="F20">
-        <v>1.539528126161999</v>
+        <v>0.6503809219168849</v>
       </c>
       <c r="G20">
-        <v>-4.937157818488155</v>
+        <v>-4.088171270975871</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.724633799149096</v>
       </c>
       <c r="E21">
-        <v>-24.03381368102622</v>
+        <v>-22.2540826397457</v>
       </c>
       <c r="F21">
-        <v>1.575384837559578</v>
+        <v>0.9645400877960002</v>
       </c>
       <c r="G21">
-        <v>-4.749186479012247</v>
+        <v>-3.018283044417089</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.001738328527987</v>
       </c>
       <c r="E22">
-        <v>-23.8493644062198</v>
+        <v>-22.61117998609456</v>
       </c>
       <c r="F22">
-        <v>1.264813330901987</v>
+        <v>1.21293433719946</v>
       </c>
       <c r="G22">
-        <v>-4.631777809172196</v>
+        <v>-3.293941748847599</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.112910628379226</v>
       </c>
       <c r="E23">
-        <v>-24.72530713352348</v>
+        <v>-23.79110558811112</v>
       </c>
       <c r="F23">
-        <v>1.432817837333366</v>
+        <v>0.8952289304689599</v>
       </c>
       <c r="G23">
-        <v>-3.194560110255138</v>
+        <v>-2.842800034196426</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.073504878127311</v>
       </c>
       <c r="E24">
-        <v>-25.73451832239888</v>
+        <v>-24.22257406308794</v>
       </c>
       <c r="F24">
-        <v>1.609200451676659</v>
+        <v>1.014628151173675</v>
       </c>
       <c r="G24">
-        <v>-3.470786466015432</v>
+        <v>-2.760438091832804</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.904269695499827</v>
       </c>
       <c r="E25">
-        <v>-25.29406988346485</v>
+        <v>-24.16799236587349</v>
       </c>
       <c r="F25">
-        <v>1.591953842350374</v>
+        <v>1.2602009812032</v>
       </c>
       <c r="G25">
-        <v>-2.694121322894867</v>
+        <v>-2.436013872585827</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.633287826083658</v>
       </c>
       <c r="E26">
-        <v>-25.5402920722099</v>
+        <v>-24.74106169459616</v>
       </c>
       <c r="F26">
-        <v>1.573019020257183</v>
+        <v>1.421164364710783</v>
       </c>
       <c r="G26">
-        <v>-3.793478200279022</v>
+        <v>-1.922853789239589</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.291703161350298</v>
       </c>
       <c r="E27">
-        <v>-26.41598120496915</v>
+        <v>-25.41019354244354</v>
       </c>
       <c r="F27">
-        <v>1.187225126486174</v>
+        <v>1.030090457114331</v>
       </c>
       <c r="G27">
-        <v>-3.041468155956125</v>
+        <v>-3.594849453178036</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.9105591971717582</v>
       </c>
       <c r="E28">
-        <v>-25.94873325685773</v>
+        <v>-24.42253788984464</v>
       </c>
       <c r="F28">
-        <v>1.141817338934317</v>
+        <v>1.153020179689777</v>
       </c>
       <c r="G28">
-        <v>-3.048266847027295</v>
+        <v>-3.142401812346204</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.520577945991849</v>
       </c>
       <c r="E29">
-        <v>-26.22535509161627</v>
+        <v>-23.84406156315682</v>
       </c>
       <c r="F29">
-        <v>1.483427772174805</v>
+        <v>1.176351975957028</v>
       </c>
       <c r="G29">
-        <v>-3.171611246668381</v>
+        <v>-3.300888094888943</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.1461130804760658</v>
       </c>
       <c r="E30">
-        <v>-26.52057084065031</v>
+        <v>-23.77783263079464</v>
       </c>
       <c r="F30">
-        <v>1.042756194703135</v>
+        <v>1.236037504063538</v>
       </c>
       <c r="G30">
-        <v>-3.93820303960145</v>
+        <v>-3.733018411824693</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.1941554232912741</v>
       </c>
       <c r="E31">
-        <v>-25.16749450647646</v>
+        <v>-23.79872700986603</v>
       </c>
       <c r="F31">
-        <v>1.132773223630552</v>
+        <v>0.7607020642543203</v>
       </c>
       <c r="G31">
-        <v>-3.526189892046655</v>
+        <v>-3.600857369853379</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.4907590248497876</v>
       </c>
       <c r="E32">
-        <v>-25.93788756160935</v>
+        <v>-22.22565740839956</v>
       </c>
       <c r="F32">
-        <v>0.9962118870746365</v>
+        <v>0.613332189826677</v>
       </c>
       <c r="G32">
-        <v>-3.776356786181839</v>
+        <v>-3.158942450227365</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.7411283121868678</v>
       </c>
       <c r="E33">
-        <v>-25.82591198482169</v>
+        <v>-23.34339800534279</v>
       </c>
       <c r="F33">
-        <v>1.197387537783719</v>
+        <v>0.9886787139135778</v>
       </c>
       <c r="G33">
-        <v>-4.110398265819549</v>
+        <v>-3.286024161224659</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.9501681814611398</v>
       </c>
       <c r="E34">
-        <v>-25.01985719687839</v>
+        <v>-22.38197127419632</v>
       </c>
       <c r="F34">
-        <v>1.278388615899066</v>
+        <v>1.328644009492106</v>
       </c>
       <c r="G34">
-        <v>-3.68044667999927</v>
+        <v>-4.076043876092163</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.127827669867898</v>
       </c>
       <c r="E35">
-        <v>-24.42541347083952</v>
+        <v>-23.51604154841122</v>
       </c>
       <c r="F35">
-        <v>0.9396178261153743</v>
+        <v>1.001727157242476</v>
       </c>
       <c r="G35">
-        <v>-4.502215494675961</v>
+        <v>-3.392401364181857</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.287683609271213</v>
       </c>
       <c r="E36">
-        <v>-24.23745915715116</v>
+        <v>-21.8055055899679</v>
       </c>
       <c r="F36">
-        <v>1.332820637937021</v>
+        <v>0.8314794318843156</v>
       </c>
       <c r="G36">
-        <v>-4.537728155613832</v>
+        <v>-4.269517824123262</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.445326292866247</v>
       </c>
       <c r="E37">
-        <v>-23.83296227336402</v>
+        <v>-22.22181726244105</v>
       </c>
       <c r="F37">
-        <v>1.114509379133628</v>
+        <v>1.017217627674826</v>
       </c>
       <c r="G37">
-        <v>-4.354088028596389</v>
+        <v>-3.485184466218274</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.614175896125787</v>
       </c>
       <c r="E38">
-        <v>-23.25517427472536</v>
+        <v>-20.98591519321567</v>
       </c>
       <c r="F38">
-        <v>1.221900585967362</v>
+        <v>1.022423088434018</v>
       </c>
       <c r="G38">
-        <v>-4.532091016974706</v>
+        <v>-4.537183472834964</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.808845511270945</v>
       </c>
       <c r="E39">
-        <v>-22.96178350071641</v>
+        <v>-20.55414331048033</v>
       </c>
       <c r="F39">
-        <v>1.090213363209519</v>
+        <v>1.166033831587758</v>
       </c>
       <c r="G39">
-        <v>-4.385052916452869</v>
+        <v>-3.663522139195655</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.035745211246206</v>
       </c>
       <c r="E40">
-        <v>-22.49267887826184</v>
+        <v>-20.62856425232239</v>
       </c>
       <c r="F40">
-        <v>1.337399852939697</v>
+        <v>1.338711986905731</v>
       </c>
       <c r="G40">
-        <v>-4.870339022651624</v>
+        <v>-4.537065348858824</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.300649171088708</v>
       </c>
       <c r="E41">
-        <v>-22.86249670809824</v>
+        <v>-19.4255977745548</v>
       </c>
       <c r="F41">
-        <v>1.423058012593583</v>
+        <v>1.202071127079147</v>
       </c>
       <c r="G41">
-        <v>-4.187769470191256</v>
+        <v>-3.83562220998853</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.597458746835509</v>
       </c>
       <c r="E42">
-        <v>-22.14343843431629</v>
+        <v>-19.37399128476338</v>
       </c>
       <c r="F42">
-        <v>1.537086099058546</v>
+        <v>1.254866295129171</v>
       </c>
       <c r="G42">
-        <v>-4.495406959940114</v>
+        <v>-3.400574887086433</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.917143361057185</v>
       </c>
       <c r="E43">
-        <v>-22.11995376811251</v>
+        <v>-19.2423440168864</v>
       </c>
       <c r="F43">
-        <v>1.762309255470898</v>
+        <v>1.237432474769853</v>
       </c>
       <c r="G43">
-        <v>-4.047897557555246</v>
+        <v>-3.63092976544569</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.242749794090094</v>
       </c>
       <c r="E44">
-        <v>-21.28421936152294</v>
+        <v>-17.79979862174301</v>
       </c>
       <c r="F44">
-        <v>1.602455884283066</v>
+        <v>1.420185234440674</v>
       </c>
       <c r="G44">
-        <v>-4.569093352500563</v>
+        <v>-3.233084932584578</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.554943967446596</v>
       </c>
       <c r="E45">
-        <v>-20.87846356196167</v>
+        <v>-17.94229158486836</v>
       </c>
       <c r="F45">
-        <v>1.672630200443823</v>
+        <v>1.341922738958982</v>
       </c>
       <c r="G45">
-        <v>-4.306139537948224</v>
+        <v>-3.425600763920318</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.836208452503134</v>
       </c>
       <c r="E46">
-        <v>-19.81343440246772</v>
+        <v>-17.99453206102085</v>
       </c>
       <c r="F46">
-        <v>1.958029278465143</v>
+        <v>1.230117990603133</v>
       </c>
       <c r="G46">
-        <v>-5.203058170000877</v>
+        <v>-3.732408104614637</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.068744829953783</v>
       </c>
       <c r="E47">
-        <v>-19.67106823661458</v>
+        <v>-17.74104619996749</v>
       </c>
       <c r="F47">
-        <v>1.933536111099167</v>
+        <v>1.687260825512068</v>
       </c>
       <c r="G47">
-        <v>-4.618472455748647</v>
+        <v>-3.321868225540033</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.245741561582144</v>
       </c>
       <c r="E48">
-        <v>-19.19061978677079</v>
+        <v>-15.57051238029903</v>
       </c>
       <c r="F48">
-        <v>1.548732944741907</v>
+        <v>1.387572409792457</v>
       </c>
       <c r="G48">
-        <v>-4.785102730201928</v>
+        <v>-3.695825765448387</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.359482369271315</v>
       </c>
       <c r="E49">
-        <v>-18.05303994519995</v>
+        <v>-17.36712557268014</v>
       </c>
       <c r="F49">
-        <v>1.959417622232234</v>
+        <v>0.8547416452897313</v>
       </c>
       <c r="G49">
-        <v>-4.883473752554081</v>
+        <v>-4.307845773159135</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.41735866640486</v>
       </c>
       <c r="E50">
-        <v>-17.91445958361722</v>
+        <v>-15.06265307728681</v>
       </c>
       <c r="F50">
-        <v>1.717955151255401</v>
+        <v>1.169377122425456</v>
       </c>
       <c r="G50">
-        <v>-4.538824083614687</v>
+        <v>-3.493456425769635</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.425841163968999</v>
       </c>
       <c r="E51">
-        <v>-17.98222819714201</v>
+        <v>-13.95999682726313</v>
       </c>
       <c r="F51">
-        <v>1.256905735674863</v>
+        <v>1.249273158425469</v>
       </c>
       <c r="G51">
-        <v>-4.619942443007279</v>
+        <v>-3.6594731117913</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.402392540469164</v>
       </c>
       <c r="E52">
-        <v>-16.95559144028508</v>
+        <v>-14.99174623127471</v>
       </c>
       <c r="F52">
-        <v>1.602654692459738</v>
+        <v>1.398488635426549</v>
       </c>
       <c r="G52">
-        <v>-4.893481478310387</v>
+        <v>-3.712156405149744</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.363019343848424</v>
       </c>
       <c r="E53">
-        <v>-17.05976898483154</v>
+        <v>-15.08444862268573</v>
       </c>
       <c r="F53">
-        <v>1.76894116489771</v>
+        <v>1.302789006115928</v>
       </c>
       <c r="G53">
-        <v>-4.571196615520168</v>
+        <v>-4.378707033956903</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.325208457454299</v>
       </c>
       <c r="E54">
-        <v>-15.62741265620541</v>
+        <v>-13.43396022958412</v>
       </c>
       <c r="F54">
-        <v>1.172735323876406</v>
+        <v>1.397917061918618</v>
       </c>
       <c r="G54">
-        <v>-5.121362315613823</v>
+        <v>-3.834188316167052</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.305557747212337</v>
       </c>
       <c r="E55">
-        <v>-15.45659861663608</v>
+        <v>-12.79447177259095</v>
       </c>
       <c r="F55">
-        <v>1.418601395966521</v>
+        <v>1.369065025279111</v>
       </c>
       <c r="G55">
-        <v>-4.74650572099818</v>
+        <v>-4.943461045103849</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.311002864610707</v>
       </c>
       <c r="E56">
-        <v>-15.64680811038026</v>
+        <v>-13.01294800109101</v>
       </c>
       <c r="F56">
-        <v>1.283786257895707</v>
+        <v>1.198799075838089</v>
       </c>
       <c r="G56">
-        <v>-5.038324441608955</v>
+        <v>-3.499946682014217</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.35090676161095</v>
       </c>
       <c r="E57">
-        <v>-15.37509061297202</v>
+        <v>-12.58557779509113</v>
       </c>
       <c r="F57">
-        <v>1.074423023777355</v>
+        <v>1.195449158061168</v>
       </c>
       <c r="G57">
-        <v>-5.03516790646877</v>
+        <v>-4.508436690752669</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.41793545267272</v>
       </c>
       <c r="E58">
-        <v>-14.74582292181416</v>
+        <v>-13.1687456208509</v>
       </c>
       <c r="F58">
-        <v>1.158780646608845</v>
+        <v>1.259950814247554</v>
       </c>
       <c r="G58">
-        <v>-5.453179127034229</v>
+        <v>-4.020860291905421</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.512059594270927</v>
       </c>
       <c r="E59">
-        <v>-14.62206425565854</v>
+        <v>-11.39014216959829</v>
       </c>
       <c r="F59">
-        <v>1.316629368681902</v>
+        <v>1.210583430510315</v>
       </c>
       <c r="G59">
-        <v>-6.181580782236921</v>
+        <v>-4.703164065419475</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.618313720952785</v>
       </c>
       <c r="E60">
-        <v>-14.24672621600679</v>
+        <v>-11.83456208023705</v>
       </c>
       <c r="F60">
-        <v>1.277540367678599</v>
+        <v>0.9382510199007551</v>
       </c>
       <c r="G60">
-        <v>-6.302982698714816</v>
+        <v>-4.780909329048958</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.729038697838563</v>
       </c>
       <c r="E61">
-        <v>-13.34496212991138</v>
+        <v>-11.15190368052876</v>
       </c>
       <c r="F61">
-        <v>1.380233074603654</v>
+        <v>1.190744031213267</v>
       </c>
       <c r="G61">
-        <v>-6.5850594725156</v>
+        <v>-4.537114567182216</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.830975015939737</v>
       </c>
       <c r="E62">
-        <v>-13.89986322091527</v>
+        <v>-11.4470016892386</v>
       </c>
       <c r="F62">
-        <v>1.042456325703322</v>
+        <v>0.8502419535577244</v>
       </c>
       <c r="G62">
-        <v>-5.656588613947326</v>
+        <v>-5.26384608061115</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.914734765137737</v>
       </c>
       <c r="E63">
-        <v>-13.45174807548625</v>
+        <v>-12.0785970160364</v>
       </c>
       <c r="F63">
-        <v>0.7654949980469182</v>
+        <v>0.7625973688719255</v>
       </c>
       <c r="G63">
-        <v>-6.340762683750262</v>
+        <v>-5.988448081248005</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.973066628607207</v>
       </c>
       <c r="E64">
-        <v>-13.7893593981801</v>
+        <v>-10.71046803426105</v>
       </c>
       <c r="F64">
-        <v>0.6487175601720635</v>
+        <v>0.800238383655135</v>
       </c>
       <c r="G64">
-        <v>-6.94663696348017</v>
+        <v>-5.001338512190895</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.996071679675535</v>
       </c>
       <c r="E65">
-        <v>-13.31679502158367</v>
+        <v>-10.83351120152347</v>
       </c>
       <c r="F65">
-        <v>0.8537674852240391</v>
+        <v>0.6688460596926886</v>
       </c>
       <c r="G65">
-        <v>-6.732468351073654</v>
+        <v>-5.656358928438165</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.982999390285409</v>
       </c>
       <c r="E66">
-        <v>-12.65313357033756</v>
+        <v>-11.15091194472108</v>
       </c>
       <c r="F66">
-        <v>0.8527419663793733</v>
+        <v>0.9247154965390112</v>
       </c>
       <c r="G66">
-        <v>-6.851051698231986</v>
+        <v>-5.97139885402513</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.927078255238856</v>
       </c>
       <c r="E67">
-        <v>-13.1480233237918</v>
+        <v>-11.85249483730743</v>
       </c>
       <c r="F67">
-        <v>0.7392523187262299</v>
+        <v>0.9189715969679993</v>
       </c>
       <c r="G67">
-        <v>-6.885691554235043</v>
+        <v>-6.616798728660108</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.835401329425448</v>
       </c>
       <c r="E68">
-        <v>-13.35987439481864</v>
+        <v>-11.49848591023181</v>
       </c>
       <c r="F68">
-        <v>0.7055029740013724</v>
+        <v>1.119799333367906</v>
       </c>
       <c r="G68">
-        <v>-6.764394636847051</v>
+        <v>-5.766401255877263</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.707992600569383</v>
       </c>
       <c r="E69">
-        <v>-13.09715044678963</v>
+        <v>-10.81206887709715</v>
       </c>
       <c r="F69">
-        <v>0.4641912658918484</v>
+        <v>0.6151156648449043</v>
       </c>
       <c r="G69">
-        <v>-7.512467215298614</v>
+        <v>-6.407122108568473</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.555541462292674</v>
       </c>
       <c r="E70">
-        <v>-13.65577394342783</v>
+        <v>-10.50660971985776</v>
       </c>
       <c r="F70">
-        <v>0.6021707674413564</v>
+        <v>0.4317234055391218</v>
       </c>
       <c r="G70">
-        <v>-6.69443571197813</v>
+        <v>-6.0219198223759</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.384580017035849</v>
       </c>
       <c r="E71">
-        <v>-13.13607268088556</v>
+        <v>-11.22886056781511</v>
       </c>
       <c r="F71">
-        <v>0.5817283166750703</v>
+        <v>0.4922248755373893</v>
       </c>
       <c r="G71">
-        <v>-7.366400356358373</v>
+        <v>-5.316936245442966</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.205168706540984</v>
       </c>
       <c r="E72">
-        <v>-13.49243188597116</v>
+        <v>-10.92949673659005</v>
       </c>
       <c r="F72">
-        <v>0.4605878676896706</v>
+        <v>0.8284177859635686</v>
       </c>
       <c r="G72">
-        <v>-6.869544662941016</v>
+        <v>-6.853801361898801</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.028006710916142</v>
       </c>
       <c r="E73">
-        <v>-12.98124868303732</v>
+        <v>-11.07668572726136</v>
       </c>
       <c r="F73">
-        <v>0.7111789474453546</v>
+        <v>0.7164423939227427</v>
       </c>
       <c r="G73">
-        <v>-6.524228906025054</v>
+        <v>-5.640307192569361</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.859306788799425</v>
       </c>
       <c r="E74">
-        <v>-13.31057742677114</v>
+        <v>-10.90834876297423</v>
       </c>
       <c r="F74">
-        <v>0.4690049088695163</v>
+        <v>0.7185381634518254</v>
       </c>
       <c r="G74">
-        <v>-6.35129212373452</v>
+        <v>-6.588488349045219</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.710456731958511</v>
       </c>
       <c r="E75">
-        <v>-13.52936611997772</v>
+        <v>-10.99596567807463</v>
       </c>
       <c r="F75">
-        <v>0.3083737006904558</v>
+        <v>0.4429834036453755</v>
       </c>
       <c r="G75">
-        <v>-6.813645772454316</v>
+        <v>-5.860047319183814</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.581505226651026</v>
       </c>
       <c r="E76">
-        <v>-13.81399429678183</v>
+        <v>-12.00351038851522</v>
       </c>
       <c r="F76">
-        <v>0.67788023458762</v>
+        <v>0.3474544180197309</v>
       </c>
       <c r="G76">
-        <v>-5.926193464600661</v>
+        <v>-5.029530767829644</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.481031039134656</v>
       </c>
       <c r="E77">
-        <v>-13.71117529443767</v>
+        <v>-11.18962586901266</v>
       </c>
       <c r="F77">
-        <v>0.3442652035189528</v>
+        <v>0.5722136886865151</v>
       </c>
       <c r="G77">
-        <v>-6.775832975203275</v>
+        <v>-5.959182866159318</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.403951851867089</v>
       </c>
       <c r="E78">
-        <v>-14.11991988684401</v>
+        <v>-11.86606214543441</v>
       </c>
       <c r="F78">
-        <v>0.6265579037797739</v>
+        <v>0.1895634492091311</v>
       </c>
       <c r="G78">
-        <v>-6.059765431842536</v>
+        <v>-4.877249275255815</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.350452409431687</v>
       </c>
       <c r="E79">
-        <v>-14.0536728405858</v>
+        <v>-11.87902716651837</v>
       </c>
       <c r="F79">
-        <v>0.3481088282679425</v>
+        <v>0.5233607211064143</v>
       </c>
       <c r="G79">
-        <v>-5.745417844004614</v>
+        <v>-4.452537800265969</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.312169030834358</v>
       </c>
       <c r="E80">
-        <v>-14.62402055642985</v>
+        <v>-13.28406773993023</v>
       </c>
       <c r="F80">
-        <v>0.3834884000415094</v>
+        <v>0.1068923824097405</v>
       </c>
       <c r="G80">
-        <v>-5.658019226547244</v>
+        <v>-4.962872751849524</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.28286005368792</v>
       </c>
       <c r="E81">
-        <v>-15.38878924684523</v>
+        <v>-13.04213401607045</v>
       </c>
       <c r="F81">
-        <v>0.5212715785165539</v>
+        <v>0.1904290931450566</v>
       </c>
       <c r="G81">
-        <v>-5.245933892118141</v>
+        <v>-4.420007769725633</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.255924088361409</v>
       </c>
       <c r="E82">
-        <v>-16.40283684596082</v>
+        <v>-13.32572517232679</v>
       </c>
       <c r="F82">
-        <v>0.5056510544019637</v>
+        <v>0.0929078839156792</v>
       </c>
       <c r="G82">
-        <v>-5.16693848307451</v>
+        <v>-4.387776330347208</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.222154312756467</v>
       </c>
       <c r="E83">
-        <v>-16.05452021071284</v>
+        <v>-15.45547102660817</v>
       </c>
       <c r="F83">
-        <v>0.2395181454349553</v>
+        <v>0.3950159608188673</v>
       </c>
       <c r="G83">
-        <v>-5.068619960267308</v>
+        <v>-4.708702767411817</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.177714065977033</v>
       </c>
       <c r="E84">
-        <v>-18.19242184668203</v>
+        <v>-15.772998567078</v>
       </c>
       <c r="F84">
-        <v>0.2531414757413959</v>
+        <v>-0.1103113491761095</v>
       </c>
       <c r="G84">
-        <v>-4.963699619682505</v>
+        <v>-4.654903858723162</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.113523559819122</v>
       </c>
       <c r="E85">
-        <v>-18.20797262642438</v>
+        <v>-16.42568752580353</v>
       </c>
       <c r="F85">
-        <v>0.1456318123690621</v>
+        <v>0.1847564331706856</v>
       </c>
       <c r="G85">
-        <v>-4.633323264526694</v>
+        <v>-3.837525318493008</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.031918533864049</v>
       </c>
       <c r="E86">
-        <v>-19.91765723175425</v>
+        <v>-17.20441750158455</v>
       </c>
       <c r="F86">
-        <v>0.2534148369843198</v>
+        <v>-0.01991989818262746</v>
       </c>
       <c r="G86">
-        <v>-4.628611430367331</v>
+        <v>-3.620459387449502</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.931015598593248</v>
       </c>
       <c r="E87">
-        <v>-20.07023510649469</v>
+        <v>-20.07657949857943</v>
       </c>
       <c r="F87">
-        <v>0.1869946818930499</v>
+        <v>0.08609042019063927</v>
       </c>
       <c r="G87">
-        <v>-4.371662251268775</v>
+        <v>-3.816932371985933</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.819898682375903</v>
       </c>
       <c r="E88">
-        <v>-21.46521793913552</v>
+        <v>-18.8738802007783</v>
       </c>
       <c r="F88">
-        <v>0.3823328275146041</v>
+        <v>0.1626191426982716</v>
       </c>
       <c r="G88">
-        <v>-4.548588998975593</v>
+        <v>-2.92597900072835</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.705336752693877</v>
       </c>
       <c r="E89">
-        <v>-21.87955066846732</v>
+        <v>-20.33541801590986</v>
       </c>
       <c r="F89">
-        <v>0.2225639498018578</v>
+        <v>-0.2389551500960671</v>
       </c>
       <c r="G89">
-        <v>-3.722262567552834</v>
+        <v>-3.833604258729471</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.598530397518506</v>
       </c>
       <c r="E90">
-        <v>-24.01227625864574</v>
+        <v>-22.21591666080906</v>
       </c>
       <c r="F90">
-        <v>-0.002505958640976257</v>
+        <v>-0.4228278624954734</v>
       </c>
       <c r="G90">
-        <v>-4.044944458151746</v>
+        <v>-3.701059313835702</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.51063546014651</v>
       </c>
       <c r="E91">
-        <v>-24.48669730958532</v>
+        <v>-23.9548053950144</v>
       </c>
       <c r="F91">
-        <v>0.1674684054742599</v>
+        <v>-0.4771041514617026</v>
       </c>
       <c r="G91">
-        <v>-3.976485051535491</v>
+        <v>-3.34020697283577</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.449754127156056</v>
       </c>
       <c r="E92">
-        <v>-26.93797840383331</v>
+        <v>-25.56948261566335</v>
       </c>
       <c r="F92">
-        <v>-0.1161364287525956</v>
+        <v>0.2823695911817737</v>
       </c>
       <c r="G92">
-        <v>-3.54938812847193</v>
+        <v>-2.924249796966522</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.428583923774172</v>
       </c>
       <c r="E93">
-        <v>-29.32265470237649</v>
+        <v>-28.54372547373914</v>
       </c>
       <c r="F93">
-        <v>-0.2605440613478279</v>
+        <v>-0.1588859853088697</v>
       </c>
       <c r="G93">
-        <v>-4.012286459970593</v>
+        <v>-3.37707477827769</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.450865541878171</v>
       </c>
       <c r="E94">
-        <v>-30.97705343278372</v>
+        <v>-29.56401557427431</v>
       </c>
       <c r="F94">
-        <v>-0.02625690881404368</v>
+        <v>-0.1402311513978249</v>
       </c>
       <c r="G94">
-        <v>-3.739318357218827</v>
+        <v>-3.72423458171006</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.527255815474637</v>
       </c>
       <c r="E95">
-        <v>-32.58709576028583</v>
+        <v>-32.21722811723534</v>
       </c>
       <c r="F95">
-        <v>0.02819996424599582</v>
+        <v>-0.7253708322851312</v>
       </c>
       <c r="G95">
-        <v>-4.044193058414633</v>
+        <v>-3.332177823679808</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.659168605946852</v>
       </c>
       <c r="E96">
-        <v>-33.99068722201524</v>
+        <v>-34.02648480904587</v>
       </c>
       <c r="F96">
-        <v>-0.1930627676135717</v>
+        <v>-0.331694194309083</v>
       </c>
       <c r="G96">
-        <v>-3.950592932209913</v>
+        <v>-3.723814585350451</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.846474788274602</v>
       </c>
       <c r="E97">
-        <v>-37.05568522767875</v>
+        <v>-36.74435037541441</v>
       </c>
       <c r="F97">
-        <v>-0.3286134959380717</v>
+        <v>-0.5403392338892085</v>
       </c>
       <c r="G97">
-        <v>-4.068470816732964</v>
+        <v>-3.651834428000913</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.091727260058653</v>
       </c>
       <c r="E98">
-        <v>-39.28364689047548</v>
+        <v>-38.14280881185613</v>
       </c>
       <c r="F98">
-        <v>-0.3768335908224337</v>
+        <v>-0.4965807258363246</v>
       </c>
       <c r="G98">
-        <v>-4.234756562922504</v>
+        <v>-3.040874254853866</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.376407337005367</v>
       </c>
       <c r="E99">
-        <v>-42.37700446461204</v>
+        <v>-41.35522223189133</v>
       </c>
       <c r="F99">
-        <v>-0.4598608556050281</v>
+        <v>-0.7490256918394739</v>
       </c>
       <c r="G99">
-        <v>-4.626855976833029</v>
+        <v>-3.822749977810828</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.710681179565051</v>
       </c>
       <c r="E100">
-        <v>-43.4173624977122</v>
+        <v>-43.99037295627276</v>
       </c>
       <c r="F100">
-        <v>-0.4961814527481752</v>
+        <v>-0.862467294183255</v>
       </c>
       <c r="G100">
-        <v>-5.062306889986937</v>
+        <v>-3.936851176318959</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.047755630407196</v>
       </c>
       <c r="E101">
-        <v>-46.33206271529814</v>
+        <v>-46.56785356416652</v>
       </c>
       <c r="F101">
-        <v>-0.6578456350785268</v>
+        <v>-0.8780066382923709</v>
       </c>
       <c r="G101">
-        <v>-5.372713730731967</v>
+        <v>-4.668842487907683</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.432789811390194</v>
       </c>
       <c r="E102">
-        <v>-49.33330546752616</v>
+        <v>-48.47279011904811</v>
       </c>
       <c r="F102">
-        <v>-0.6798561853383124</v>
+        <v>-0.6902811891025442</v>
       </c>
       <c r="G102">
-        <v>-5.552462328979908</v>
+        <v>-4.030913954763561</v>
       </c>
     </row>
   </sheetData>
